--- a/astro-site/public/dl/restaurant-checklist-templates/05-restaurant-cleaning-schedule.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/05-restaurant-cleaning-schedule.xlsx
@@ -802,7 +802,7 @@
     <row r="14" ht="47" customHeight="1">
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>▸ At the bottom of "Weekly FIFO Check" there is an editable table of freezer shelf life by product family: one single rule for the whole freezer either throws out good product or lets old product slip through.</t>
+          <t>▸ At the bottom of "Weekly FIFO Check" there is an editable table of freezer shelf life by food group: one single rule for the whole freezer either throws out good product or lets old product slip through.</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
     <row r="34" ht="31" customHeight="1">
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the FRAME of the day.</t>
+          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the BACKBONE of the day.</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="B23" s="37" t="inlineStr">
         <is>
-          <t>Calibrate thermometers and probes against a known reference: ice-point method (32 °F)</t>
+          <t>Thermometers: ice-point check (32 °F) weekly and after any drop; send the reference thermometer for certified calibration yearly</t>
         </is>
       </c>
       <c r="C23" s="38" t="n"/>
